--- a/tests/ITER_2D_APEC_evol_fine/input_template.xlsx
+++ b/tests/ITER_2D_APEC_evol_fine/input_template.xlsx
@@ -4,11 +4,11 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
-    <sheet r:id="rId2" sheetId="2" name="cp"/>
+    <sheet r:id="rId2" sheetId="2" name="dof_couplings"/>
     <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
     <sheet r:id="rId4" sheetId="4" name="materials"/>
     <sheet r:id="rId5" sheetId="5" name="real_constants"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
   <si>
     <t>time_step_number</t>
   </si>
@@ -328,7 +328,16 @@
     <t>dof4</t>
   </si>
   <si>
-    <t>CP_ID</t>
+    <t>cp_id</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
   <si>
     <t>ansys_etype</t>
@@ -362,7 +371,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,12 +382,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -410,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -440,12 +443,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -764,25 +761,25 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -790,7 +787,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -813,7 +810,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
@@ -836,7 +833,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -855,13 +852,27 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="A5" s="1">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1078,53 +1089,212 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="7" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+      <c r="A1" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="1">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="1">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="1">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="1">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="1">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="1">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="1">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="1">
+        <v>15</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="1">
+        <v>16</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="1">
+        <v>16</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1205,7 +1375,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="20.14785714285714" customWidth="1" bestFit="1"/>
@@ -1223,7 +1393,7 @@
     <col min="13" max="13" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
@@ -1264,7 +1434,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
         <v>21</v>
       </c>
@@ -1305,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1">
         <v>23</v>
       </c>
@@ -1346,7 +1516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1">
         <v>24</v>
       </c>
@@ -1384,6 +1554,47 @@
         <v>0</v>
       </c>
       <c r="M4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1">
+        <v>25</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1e-8</v>
+      </c>
+      <c r="F5" s="9">
+        <v>1e-8</v>
+      </c>
+      <c r="G5" s="9">
+        <v>1e-8</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1397,7 +1608,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="21.14785714285714" customWidth="1" bestFit="1"/>
@@ -1409,7 +1620,7 @@
     <col min="7" max="7" style="4" width="6.2907142857142855" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="4" width="6.2907142857142855" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="4" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="10" width="12.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="4" width="6.2907142857142855" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="4" width="6.2907142857142855" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="4" width="6.2907142857142855" customWidth="1" bestFit="1"/>
@@ -1452,7 +1663,7 @@
       <c r="I1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="9" t="s">
         <v>65</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1485,10 +1696,10 @@
       <c r="T1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="U1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1497,19 +1708,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="9">
         <v>0.9437519</v>
       </c>
       <c r="D2" s="1">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
+      <c r="F2" s="2">
+        <v>3.94</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1518,13 +1729,13 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0.0162797144</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
@@ -1556,7 +1767,7 @@
       <c r="U2" s="1">
         <v>0</v>
       </c>
-      <c r="V2" s="11">
+      <c r="V2" s="1">
         <v>5732500</v>
       </c>
     </row>
@@ -1565,19 +1776,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="9">
         <v>0.41453946</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
+      <c r="F3" s="2">
+        <v>8.29</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1586,13 +1797,13 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0.01688462455</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1624,7 +1835,7 @@
       <c r="U3" s="1">
         <v>1</v>
       </c>
-      <c r="V3" s="11">
+      <c r="V3" s="1">
         <v>-2883400</v>
       </c>
     </row>
@@ -1633,19 +1844,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="9">
         <v>0.66413094</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
+      <c r="F4" s="2">
+        <v>12</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1654,13 +1865,13 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0.03926740844</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -1692,7 +1903,7 @@
       <c r="U4" s="1">
         <v>1</v>
       </c>
-      <c r="V4" s="11">
+      <c r="V4" s="1">
         <v>-5808400</v>
       </c>
     </row>
@@ -1701,19 +1912,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="9">
         <v>0.60871516</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
+      <c r="F5" s="2">
+        <v>12</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1722,13 +1933,13 @@
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0.0356938854</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -1760,7 +1971,7 @@
       <c r="U5" s="1">
         <v>1</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="1">
         <v>-4776200</v>
       </c>
     </row>
@@ -1769,19 +1980,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="9">
         <v>0.7749625</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
+      <c r="F6" s="2">
+        <v>8.39</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1790,13 +2001,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0.03198199512</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -1828,7 +2039,7 @@
       <c r="U6" s="1">
         <v>-1</v>
       </c>
-      <c r="V6" s="11">
+      <c r="V6" s="1">
         <v>-7813300</v>
       </c>
     </row>
@@ -1837,19 +2048,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="9">
         <v>1.7265925</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
+      <c r="F7" s="2">
+        <v>4.33</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1858,13 +2069,13 @@
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0.03318021032</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -1896,7 +2107,7 @@
       <c r="U7" s="1">
         <v>0</v>
       </c>
-      <c r="V7" s="11">
+      <c r="V7" s="1">
         <v>16941000</v>
       </c>
     </row>
@@ -1905,7 +2116,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="9">
         <v>28.6027095</v>
@@ -1916,7 +2127,7 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>0</v>
       </c>
       <c r="G8" s="1">
@@ -1928,7 +2139,7 @@
       <c r="I8" s="1">
         <v>0</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="9">
         <v>0</v>
       </c>
       <c r="K8" s="1">
@@ -1964,75 +2175,483 @@
       <c r="U8" s="1">
         <v>0</v>
       </c>
-      <c r="V8" s="11">
+      <c r="V8" s="1">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1.55608</v>
+      </c>
+      <c r="D9" s="1">
+        <v>553</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0.02094228464</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2">
+        <v>-4820400</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="1">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1.55608</v>
+      </c>
+      <c r="D10" s="1">
+        <v>553</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0.02094228464</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>-4048000</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="1">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1.55608</v>
+      </c>
+      <c r="D11" s="1">
+        <v>553</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0.02094228464</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
+        <v>-20804000</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="1">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1.55608</v>
+      </c>
+      <c r="D12" s="1">
+        <v>553</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0.02094228464</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>-20804000</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="1">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1.55608</v>
+      </c>
+      <c r="D13" s="1">
+        <v>553</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0.02094228464</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
+        <v>-10297000</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="1">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1.55608</v>
+      </c>
+      <c r="D14" s="1">
+        <v>553</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0.02094228464</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
+        <v>5301200</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="1">
         <v>20</v>
       </c>
-      <c r="B9" s="1">
-        <v>0</v>
-      </c>
-      <c r="C9" s="9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
-      <c r="U9" s="1">
-        <v>0</v>
-      </c>
-      <c r="V9" s="11">
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
         <v>0</v>
       </c>
     </row>

--- a/tests/ITER_2D_APEC_evol_fine/input_template.xlsx
+++ b/tests/ITER_2D_APEC_evol_fine/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="112">
   <si>
     <t>time_step_number</t>
   </si>
@@ -254,9 +254,6 @@
   </si>
   <si>
     <t>CPSIGN</t>
-  </si>
-  <si>
-    <t>CURR</t>
   </si>
   <si>
     <t>ansys_material_type</t>
@@ -761,25 +758,25 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -787,7 +784,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -810,7 +807,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
@@ -833,7 +830,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -856,7 +853,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" s="1">
         <v>8</v>
@@ -1098,10 +1095,10 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -1109,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -1117,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -1125,7 +1122,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -1133,7 +1130,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
@@ -1141,7 +1138,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
@@ -1149,7 +1146,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
@@ -1157,7 +1154,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
@@ -1165,7 +1162,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
@@ -1173,7 +1170,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
@@ -1181,7 +1178,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
@@ -1189,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
@@ -1197,7 +1194,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
@@ -1205,7 +1202,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
@@ -1213,7 +1210,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
@@ -1221,7 +1218,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
@@ -1229,7 +1226,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -1237,7 +1234,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
@@ -1245,7 +1242,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
@@ -1253,7 +1250,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
@@ -1261,7 +1258,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
@@ -1269,7 +1266,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -1277,7 +1274,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
@@ -1285,7 +1282,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
@@ -1293,7 +1290,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1323,34 +1320,34 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
@@ -1395,43 +1392,43 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -1608,7 +1605,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="21.14785714285714" customWidth="1" bestFit="1"/>
@@ -1632,7 +1629,6 @@
     <col min="19" max="19" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="20" max="20" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -1699,9 +1695,6 @@
       <c r="U1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
@@ -1766,9 +1759,6 @@
       </c>
       <c r="U2" s="1">
         <v>0</v>
-      </c>
-      <c r="V2" s="1">
-        <v>5732500</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -1835,9 +1825,6 @@
       <c r="U3" s="1">
         <v>1</v>
       </c>
-      <c r="V3" s="1">
-        <v>-2883400</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1">
@@ -1903,9 +1890,6 @@
       <c r="U4" s="1">
         <v>1</v>
       </c>
-      <c r="V4" s="1">
-        <v>-5808400</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1">
@@ -1971,9 +1955,6 @@
       <c r="U5" s="1">
         <v>1</v>
       </c>
-      <c r="V5" s="1">
-        <v>-4776200</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1">
@@ -2039,9 +2020,6 @@
       <c r="U6" s="1">
         <v>-1</v>
       </c>
-      <c r="V6" s="1">
-        <v>-7813300</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1">
@@ -2107,9 +2085,6 @@
       <c r="U7" s="1">
         <v>0</v>
       </c>
-      <c r="V7" s="1">
-        <v>16941000</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1">
@@ -2175,9 +2150,6 @@
       <c r="U8" s="1">
         <v>0</v>
       </c>
-      <c r="V8" s="1">
-        <v>0</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1">
@@ -2243,9 +2215,6 @@
       <c r="U9" s="1">
         <v>0</v>
       </c>
-      <c r="V9" s="2">
-        <v>-4820400</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1">
@@ -2311,9 +2280,6 @@
       <c r="U10" s="1">
         <v>0</v>
       </c>
-      <c r="V10" s="1">
-        <v>-4048000</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1">
@@ -2379,9 +2345,6 @@
       <c r="U11" s="1">
         <v>0</v>
       </c>
-      <c r="V11" s="1">
-        <v>-20804000</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1">
@@ -2447,9 +2410,6 @@
       <c r="U12" s="1">
         <v>0</v>
       </c>
-      <c r="V12" s="1">
-        <v>-20804000</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1">
@@ -2515,9 +2475,6 @@
       <c r="U13" s="1">
         <v>0</v>
       </c>
-      <c r="V13" s="1">
-        <v>-10297000</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1">
@@ -2583,9 +2540,6 @@
       <c r="U14" s="1">
         <v>0</v>
       </c>
-      <c r="V14" s="1">
-        <v>5301200</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1">
@@ -2649,9 +2603,6 @@
         <v>0</v>
       </c>
       <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
         <v>0</v>
       </c>
     </row>

--- a/tests/ITER_2D_APEC_evol_fine/input_template.xlsx
+++ b/tests/ITER_2D_APEC_evol_fine/input_template.xlsx
@@ -224,10 +224,10 @@
     <t>VARIABLE</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>E</t>
+    <t>VOLT</t>
+  </si>
+  <si>
+    <t>EMF</t>
   </si>
   <si>
     <t>TYPE_ID</t>
@@ -306,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -324,9 +324,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -676,7 +673,7 @@
       <c r="A2" s="3">
         <v>21</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3">
@@ -699,7 +696,7 @@
       <c r="A3" s="3">
         <v>23</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="3">
         <v>0</v>
       </c>
       <c r="C3" s="3">
@@ -722,7 +719,7 @@
       <c r="A4" s="3">
         <v>24</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
@@ -745,11 +742,11 @@
       <c r="A5" s="3">
         <v>25</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -2292,7 +2289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>21</v>
       </c>

--- a/tests/ITER_2D_APEC_evol_fine/input_template.xlsx
+++ b/tests/ITER_2D_APEC_evol_fine/input_template.xlsx
@@ -955,22 +955,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
@@ -987,22 +987,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
@@ -1028,13 +1028,13 @@
         <v>8e-07</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -1060,13 +1060,13 @@
         <v>1e-08</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
